--- a/themes/debitCards.xlsx
+++ b/themes/debitCards.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,261 +450,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - "Для оформления карты «Почетный пенсионер» вам нужно обратиться в любое удобное отделение банка. Адреса и режим работы офисов «Уралсиб» вы найдете [здесь]({{$temp.officeLink}})"</t>
+          <t xml:space="preserve">    Комиссия за выпуск карты — {{$temp.debitCardData.IssueFee}} . Комиссия за обслуживание карты по истечению второго и каждого последующего месяцев — {{$temp.debitCardData.CardServiceFee}} . Комиссия не взимается при выполнении условий:</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - "Для оформления карты «Почетный пенсионер» вам нужно обратиться в любое удобное отделение банка. Адреса и режим работы офисов «Уралсиб» вы найдете [здесь]({{$temp.officeLink}})."</t>
+          <t xml:space="preserve">    Комиссия за выпуск карты — {{$temp.debitCardData.IssueFee}}. Комиссия за обслуживание карты по истечению второго и каждого последующего месяцев — {{$temp.debitCardData.CardServiceFee}}. Комиссия не взимается при выполнении условий:</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>убран лишний пробел перед точкой (дважды)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - "Ознакомиться с полным списком дебетовых карт и условиями их оформления, а также оставить заявку на получение карты вы сможете по [ссылке]({{$temp.debitCardLink}})"</t>
+          <t xml:space="preserve">  NotAuthorized: Для уточнения возможности закрытия заявки  напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - "Ознакомиться с полным списком дебетовых карт и условиями их оформления, а также оставить заявку на получение карты вы сможете по [ссылке]({{$temp.debitCardLink}})."</t>
+          <t xml:space="preserve">  NotAuthorized: Для уточнения возможности закрытия заявки напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - "Также оформить карту можно в отделении банка. Адреса и режим работы офисов «Уралсиб» вы найдете [здесь]({{$temp.officeLink}})"</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - "Также оформить карту можно в отделении банка. Адреса и режим работы офисов «Уралсиб» вы найдете [здесь]({{$temp.officeLink}})."</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Office: Оформить заявку на получение карты «Прибыль» можно, обратившись в отделение [банка]({{$temp.officeLink}})</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Office: Оформить заявку на получение карты «Прибыль» можно, обратившись в отделение [банка]({{$temp.officeLink}}).</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>60</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Mir: Оформить заявку на получение карты МИР «Классическая» можно по [ссылке]({{$temp.MirCardLink}})</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Mir: Оформить заявку на получение карты МИР «Классическая» можно по [ссылке]({{$temp.MirCardLink}}).</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>84</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Комиссия за выпуск карты — {{$temp.debitCardData.IssueFee}}</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Комиссия за выпуск карты — {{$temp.debitCardData.IssueFee}}.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>88</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Оформить заявку на дебетовую карту «Прибыль» вы можете по [ссылке]({{$temp.ProfitCardLink}})</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Оформить заявку на дебетовую карту «Прибыль» вы можете по [ссылке]({{$temp.ProfitCardLink}}).</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>89</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Также отправляю вам ссылку на подробный [тарифный план](https://uralsib.ru/api/directory-engine/files/rates/pribyl_010626_aftzmpri.pdf)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Также отправляю вам ссылку на подробный [тарифный план](https://uralsib.ru/api/directory-engine/files/rates/pribyl_010626_aftzmpri.pdf).</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>95</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Комиссия за выпуск карты — {{$temp.debitCardData.IssueFee}} . Комиссия за обслуживание карты по истечению второго и каждого последующего месяцев — {{$temp.debitCardData.CardServiceFee}} . Комиссия не взимается при выполнении условий:</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Комиссия за выпуск карты — {{$temp.debitCardData.IssueFee}}. Комиссия за обслуживание карты по истечению второго и каждого последующего месяцев — {{$temp.debitCardData.CardServiceFee}}. Комиссия не взимается при выполнении условий:</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>убран лишний пробел перед точкой (дважды)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>101</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Получить пластиковую дебетовую карту МИР «Классическая» вы можете в офисе банка Уралсиб. Также есть возможность выпустить цифровую карту в «Уралсиб Онлайн» по [ссылке]({{$temp.MirCardLink}})</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Получить пластиковую дебетовую карту МИР «Классическая» вы можете в офисе банка Уралсиб. Также есть возможность выпустить цифровую карту в «Уралсиб Онлайн» по [ссылке]({{$temp.MirCardLink}}).</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>102</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Отправляю вам ссылку на подробный [тарифный план](https://uralsib.ru/api/directory-engine/files/rates/dcard_mir_klassik_010626_nkhl5chq.pdf)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Отправляю вам ссылку на подробный [тарифный план](https://uralsib.ru/api/directory-engine/files/rates/dcard_mir_klassik_010626_nkhl5chq.pdf).</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>105</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "Ознакомиться с полным списком дебетовых карт и условиями их оформления, а также оставить заявку на получение карты вы сможете по [ссылке]({{$temp.debitCardLink}})"</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "Ознакомиться с полным списком дебетовых карт и условиями их оформления, а также оставить заявку на получение карты вы сможете по [ссылке]({{$temp.debitCardLink}})."</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>108</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NotAuthorized: Для уточнения возможности закрытия заявки  напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NotAuthorized: Для уточнения возможности закрытия заявки напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/).</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>убран двойной пробел; добавлена точка в конце предложения</t>
+          <t>убран двойной пробел</t>
         </is>
       </c>
     </row>
